--- a/高济.xlsx
+++ b/高济.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24685" windowHeight="9977"/>
+    <workbookView windowWidth="21600" windowHeight="8205"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
   <si>
     <t>业务日期</t>
   </si>
@@ -38,6 +38,9 @@
     <t>企业名称</t>
   </si>
   <si>
+    <t>城市</t>
+  </si>
+  <si>
     <t>门店编码</t>
   </si>
   <si>
@@ -71,16 +74,22 @@
     <t>供应商名称</t>
   </si>
   <si>
-    <t>2026/01/01</t>
-  </si>
-  <si>
-    <t>广州市宝芝林大药房连锁有限公司</t>
-  </si>
-  <si>
-    <t>B2R3</t>
-  </si>
-  <si>
-    <t>广州市宝芝林大药房连锁有限公司大德店</t>
+    <t>2026/01/06</t>
+  </si>
+  <si>
+    <t>2026/01</t>
+  </si>
+  <si>
+    <t>潮州市新千禧药业有限公司</t>
+  </si>
+  <si>
+    <t>潮州</t>
+  </si>
+  <si>
+    <t>AD9S</t>
+  </si>
+  <si>
+    <t>潮州市新千禧药业有限公司古德大药房</t>
   </si>
   <si>
     <t>1347215</t>
@@ -104,104 +113,36 @@
     <t>20250810</t>
   </si>
   <si>
-    <t>广州医药股份有限公司大众药品销售分公司</t>
-  </si>
-  <si>
-    <t>2026/01</t>
-  </si>
-  <si>
-    <t>惠州市百姓大药房医药连锁有限公司</t>
-  </si>
-  <si>
-    <t>ACPL</t>
-  </si>
-  <si>
-    <t>惠州市百姓大药房医药连锁有限公司康城园洲店</t>
-  </si>
-  <si>
-    <t>汕头市凯德药品连锁有限公司</t>
-  </si>
-  <si>
-    <t>ACZF</t>
-  </si>
-  <si>
-    <t>汕头市凯德药品连锁有限公司佳和分店</t>
-  </si>
-  <si>
-    <t>251001</t>
-  </si>
-  <si>
-    <t>20251007</t>
+    <t>国药控股成都医药有限公司</t>
+  </si>
+  <si>
+    <t>250202</t>
+  </si>
+  <si>
+    <t>20250205</t>
   </si>
   <si>
     <t>四川本草堂药业有限公司</t>
   </si>
   <si>
-    <t>茂名高济医药连锁有限公司</t>
-  </si>
-  <si>
-    <t>B2ZL</t>
-  </si>
-  <si>
-    <t>茂名高济医药连锁有限公司南粤高州东岸二店</t>
-  </si>
-  <si>
-    <t>清远高济百姓大药房医药连锁有限公司</t>
-  </si>
-  <si>
-    <t>BKS0</t>
-  </si>
-  <si>
-    <t>清远高济百姓大药房医药连锁有限公司英德月桂湖店</t>
-  </si>
-  <si>
-    <t>广东嘉宝华医药连锁有限公司</t>
-  </si>
-  <si>
-    <t>B4LN</t>
-  </si>
-  <si>
-    <t>广东嘉宝华医药连锁有限公司华发又一城分店</t>
-  </si>
-  <si>
-    <t>B4NX</t>
-  </si>
-  <si>
-    <t>广东嘉宝华医药连锁有限公司夏湾公交分店</t>
-  </si>
-  <si>
-    <t>250202</t>
-  </si>
-  <si>
-    <t>20250205</t>
-  </si>
-  <si>
-    <t>国药控股成都医药有限公司</t>
+    <t>2026/01/12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -351,7 +292,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,12 +301,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -551,27 +486,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -692,52 +612,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -752,100 +675,82 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1372,19 +1277,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="7"/>
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultColWidth="8.61061946902655" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="11.7027027027027" customWidth="1"/>
-    <col min="2" max="2" width="8.61261261261261" style="1"/>
-    <col min="3" max="3" width="38.8648648648649" customWidth="1"/>
+    <col min="1" max="1" width="11.6991150442478" customWidth="1"/>
+    <col min="2" max="2" width="8.61061946902655" style="1"/>
+    <col min="3" max="3" width="38.8672566371681" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1423,314 +1328,149 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <f>LEFT(A2,7)</f>
-        <v>2026/01</v>
-      </c>
-      <c r="C2" s="6" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="F2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="G2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="H2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="I2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="J2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="6">
+      <c r="K2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="2">
+        <v>3</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="2">
         <v>1</v>
       </c>
-      <c r="N2" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="O4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="6">
-        <v>2</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="6">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="6">
-        <v>1</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="6">
-        <v>1</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="6">
-        <v>2</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="6">
-        <v>1</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
